--- a/data/orders_seed.xlsx
+++ b/data/orders_seed.xlsx
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H10"/>
+  <dimension ref="A1:H8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,14 +476,14 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="D2" t="n">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -493,11 +493,11 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>S-24A</t>
+          <t>MD-S101</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -512,14 +512,14 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="D3" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -529,7 +529,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>S-24B</t>
+          <t>MD-S102</t>
         </is>
       </c>
       <c r="H3" t="n">
@@ -539,33 +539,33 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>#S-103</t>
+          <t>#M-201</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>M</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>中部物流設備</t>
+          <t>高雄港機具</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>S-24A</t>
+          <t>MD-M201</t>
         </is>
       </c>
       <c r="H4" t="n">
@@ -575,7 +575,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>#A-309</t>
+          <t>#M-202</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -584,111 +584,111 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="D5" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-11-17</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>高雄港機具</t>
+          <t>東元物流</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>M-28A</t>
+          <t>MD-M202</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>#A-311</t>
+          <t>#L-301</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>L</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>4</v>
+        <v>59</v>
       </c>
       <c r="D6" t="n">
+        <v>8</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>2026-11-02</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>台中港務</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>MD-L301</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
         <v>0</v>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>2026-10-06</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>台塑工業車輛</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>M-28A</t>
-        </is>
-      </c>
-      <c r="H6" t="n">
-        <v>3</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>#A-315</t>
+          <t>#A-311</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>L</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>36</v>
+        <v>1</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-11-12</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>東元物流</t>
+          <t>台塑工業車輛</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>M-28B</t>
+          <t>#A-311</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>#A-318</t>
+          <t>#L-302</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>L</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -704,87 +704,15 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>長榮貨櫃場</t>
+          <t>中鋼運輸</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>M-28B</t>
+          <t>MD-L302</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>#B-207</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>50</v>
-      </c>
-      <c r="D9" t="n">
-        <v>8</v>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>2026-11-17</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>台中港務</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>L-34A</t>
-        </is>
-      </c>
-      <c r="H9" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>#B-212</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>50</v>
-      </c>
-      <c r="D10" t="n">
-        <v>0</v>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>2026-12-22</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>中鋼運輸</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>L-34A</t>
-        </is>
-      </c>
-      <c r="H10" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3212,7 +3140,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H23"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3260,36 +3188,36 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>J-07-01</t>
+          <t>J-CURE-01-10030012</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>#A-309</t>
+          <t>#S-101</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>S</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>CURE-07</t>
+          <t>CURE-01</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>M-28A</t>
+          <t>MD-S101</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-10-02T16:14:00+08:00</t>
+          <t>2026-10-03T00:12:00+08:00</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="H2" t="n">
         <v>1</v>
@@ -3298,74 +3226,74 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>J-07-02</t>
+          <t>J-CURE-02-10022012</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>#A-311</t>
+          <t>#S-101</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>S</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>CURE-07</t>
+          <t>CURE-02</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>M-28A</t>
+          <t>MD-S101</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-10-03T20:44:00+08:00</t>
+          <t>2026-10-02T20:12:00+08:00</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>J-08-01</t>
+          <t>J-CURE-03-10021612</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>#A-309</t>
+          <t>#S-101</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>S</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>CURE-08</t>
+          <t>CURE-03</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>M-28A</t>
+          <t>MD-S101</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-10-02T08:30:00+08:00</t>
+          <t>2026-10-02T16:12:00+08:00</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="H4" t="n">
         <v>1</v>
@@ -3374,74 +3302,74 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>J-08-02</t>
+          <t>J-CURE-04-10021212</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>#A-315</t>
+          <t>#S-101</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>S</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>CURE-08</t>
+          <t>CURE-04</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>M-28B</t>
+          <t>MD-S101</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-10-03T13:00:00+08:00</t>
+          <t>2026-10-02T12:12:00+08:00</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J-09-01</t>
+          <t>J-CURE-05-10020812</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>#B-207</t>
+          <t>#S-101</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>S</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>CURE-09</t>
+          <t>CURE-05</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>L-34A</t>
+          <t>MD-S101</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-10-02T14:00:00+08:00</t>
+          <t>2026-10-02T08:12:00+08:00</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="H6" t="n">
         <v>1</v>
@@ -3450,74 +3378,74 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J-09-02</t>
+          <t>J-CURE-06-10020512</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>#B-207</t>
+          <t>#S-101</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>S</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>CURE-09</t>
+          <t>CURE-06</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>L-34A</t>
+          <t>MD-S101</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-10-04T00:30:00+08:00</t>
+          <t>2026-10-02T05:12:00+08:00</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J-10-01</t>
+          <t>J-CURE-07-10021614</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>#B-207</t>
+          <t>#M-201</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>M</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>CURE-10</t>
+          <t>CURE-07</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>L-34A</t>
+          <t>MD-M201</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-10-02T06:30:00+08:00</t>
+          <t>2026-10-02T16:14:00+08:00</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="H8" t="n">
         <v>1</v>
@@ -3526,12 +3454,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>J-10-07</t>
+          <t>J-CURE-08-10020612</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>#B-207</t>
+          <t>#L-301</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -3541,59 +3469,59 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>CURE-10</t>
+          <t>CURE-08</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>L-34A</t>
+          <t>MD-L301</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-10-03T17:00:00+08:00</t>
+          <t>2026-10-02T06:12:00+08:00</t>
         </is>
       </c>
       <c r="G9" t="n">
         <v>34</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>J-01-01</t>
+          <t>J-CURE-09-10020212</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>#S-101</t>
+          <t>#M-201</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>M</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>CURE-01</t>
+          <t>CURE-09</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>S-24A</t>
+          <t>MD-M201</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-10-02T07:00:00+08:00</t>
+          <t>2026-10-02T02:12:00+08:00</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="H10" t="n">
         <v>1</v>
@@ -3602,45 +3530,45 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>J-01-02</t>
+          <t>J-CURE-10-10022012</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>#S-101</t>
+          <t>#L-301</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>L</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>CURE-01</t>
+          <t>CURE-10</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>S-24A</t>
+          <t>MD-L301</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-10-03T07:30:00+08:00</t>
+          <t>2026-10-02T20:12:00+08:00</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>J-02-01</t>
+          <t>J-CURE-11-10021012</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -3655,17 +3583,17 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>CURE-02</t>
+          <t>CURE-11</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>S-24A</t>
+          <t>MD-S101</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-10-02T08:00:00+08:00</t>
+          <t>2026-10-02T10:12:00+08:00</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -3673,424 +3601,6 @@
       </c>
       <c r="H12" t="n">
         <v>1</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>J-02-02</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>#S-101</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>CURE-02</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>S-24A</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>2026-10-03T08:30:00+08:00</t>
-        </is>
-      </c>
-      <c r="G13" t="n">
-        <v>24</v>
-      </c>
-      <c r="H13" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>J-03-01</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>#S-101</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>CURE-03</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>S-24A</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>2026-10-02T09:00:00+08:00</t>
-        </is>
-      </c>
-      <c r="G14" t="n">
-        <v>24</v>
-      </c>
-      <c r="H14" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>J-03-02</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>#S-101</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>CURE-03</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>S-24A</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>2026-10-03T09:30:00+08:00</t>
-        </is>
-      </c>
-      <c r="G15" t="n">
-        <v>24</v>
-      </c>
-      <c r="H15" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>J-04-01</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>#S-101</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>CURE-04</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>S-24A</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>2026-10-02T10:00:00+08:00</t>
-        </is>
-      </c>
-      <c r="G16" t="n">
-        <v>24</v>
-      </c>
-      <c r="H16" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>J-04-02</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>#S-101</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>CURE-04</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>S-24A</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>2026-10-03T10:30:00+08:00</t>
-        </is>
-      </c>
-      <c r="G17" t="n">
-        <v>24</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>J-05-01</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>#S-102</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>CURE-05</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>S-24B</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>2026-10-02T11:00:00+08:00</t>
-        </is>
-      </c>
-      <c r="G18" t="n">
-        <v>24</v>
-      </c>
-      <c r="H18" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>J-05-02</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>#S-102</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>CURE-05</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>S-24B</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>2026-10-03T11:30:00+08:00</t>
-        </is>
-      </c>
-      <c r="G19" t="n">
-        <v>24</v>
-      </c>
-      <c r="H19" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>J-06-01</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>#S-102</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>CURE-06</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>S-24B</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>2026-10-02T12:00:00+08:00</t>
-        </is>
-      </c>
-      <c r="G20" t="n">
-        <v>24</v>
-      </c>
-      <c r="H20" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>J-06-02</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>#S-102</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>CURE-06</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>S-24B</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>2026-10-03T12:30:00+08:00</t>
-        </is>
-      </c>
-      <c r="G21" t="n">
-        <v>24</v>
-      </c>
-      <c r="H21" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>J-11-01</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>#S-102</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>CURE-11</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>S-24B</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>2026-10-02T13:00:00+08:00</t>
-        </is>
-      </c>
-      <c r="G22" t="n">
-        <v>24</v>
-      </c>
-      <c r="H22" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>J-11-02</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>#S-102</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>CURE-11</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>S-24B</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>2026-10-03T13:30:00+08:00</t>
-        </is>
-      </c>
-      <c r="G23" t="n">
-        <v>24</v>
-      </c>
-      <c r="H23" t="n">
-        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -4162,7 +3672,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>#B-207</t>
+          <t>#L-301</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -4209,7 +3719,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>#B-207</t>
+          <t>#L-301</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -4256,7 +3766,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>#B-207</t>
+          <t>#L-301</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -4303,7 +3813,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>#B-207</t>
+          <t>#L-301</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -4396,12 +3906,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-02T06:30:00+08:00</t>
+          <t>2026-10-02T02:12:00+08:00</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>CURE-10</t>
+          <t>CURE-09</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -4411,29 +3921,29 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>curing</t>
+          <t>body</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>CURI-早1</t>
+          <t>BODY-夜1</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>#B-207</t>
+          <t>#M-201</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>大胎入模，設定 128°C</t>
+          <t>中胎入模，128°C，預計 28 h</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-02T08:30:00+08:00</t>
+          <t>2026-10-02T06:12:00+08:00</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -4458,12 +3968,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>#A-309</t>
+          <t>#L-301</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>中胎入模</t>
+          <t>大胎入模，128°C，預計 34 h</t>
         </is>
       </c>
     </row>
@@ -4502,133 +4012,133 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-02T14:00:00+08:00</t>
+          <t>2026-10-02T15:40:00+08:00</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>CURE-09</t>
+          <t>A-MIX</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>入模</t>
+          <t>QC 取樣</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>curing</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>CURI-中1</t>
+          <t>qc</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>#B-207</t>
+          <t>#L-301</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>大胎入模</t>
+          <t>門尼黏度 62，合格</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-02T15:40:00+08:00</t>
+          <t>2026-10-02T16:14:00+08:00</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>A-MIX</t>
+          <t>CURE-07</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>QC 取樣</t>
+          <t>入模</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>qc</t>
+          <t>curing</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>CURI-中1</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>#B-207</t>
+          <t>#M-201</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>門尼黏度 62，合格</t>
+          <t>中胎入模，128°C，預計 28 h</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-02T16:14:00+08:00</t>
+          <t>2026-10-02T18:00:00+08:00</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>CURE-07</t>
+          <t>CURE-03</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>入模</t>
+          <t>保養</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>curing</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>CURI-中2</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>#A-309</t>
+          <t>maintenance</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>中胎入模，128°C，預計 28 h</t>
+          <t>更換疏水閥墊片</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-02T18:00:00+08:00</t>
+          <t>2026-10-02T20:12:00+08:00</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>CURE-03</t>
+          <t>CURE-10</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>保養</t>
+          <t>入模</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>maintenance</t>
+          <t>body</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>BODY-夜1</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>#L-301</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>更換疏水閥墊片</t>
+          <t>大胎入模，128°C，預計 34 h</t>
         </is>
       </c>
     </row>

--- a/data/orders_seed.xlsx
+++ b/data/orders_seed.xlsx
@@ -512,7 +512,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -652,7 +652,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>S</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -692,7 +692,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -3416,17 +3416,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J-CURE-07-10021614</t>
+          <t>J-CURE-07-10021150</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>#M-201</t>
+          <t>#S-101</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>S</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -3436,16 +3436,16 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>MD-M201</t>
+          <t>MD-S101</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-10-02T16:14:00+08:00</t>
+          <t>2026-10-02T11:50:00+08:00</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="H8" t="n">
         <v>1</v>
@@ -3568,17 +3568,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>J-CURE-11-10021012</t>
+          <t>J-CURE-11-10021612</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>#S-101</t>
+          <t>#M-201</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>M</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -3588,16 +3588,16 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>MD-S101</t>
+          <t>MD-M201</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-10-02T10:12:00+08:00</t>
+          <t>2026-10-02T16:12:00+08:00</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="H12" t="n">
         <v>1</v>
@@ -4012,69 +4012,69 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-02T15:40:00+08:00</t>
+          <t>2026-10-02T11:50:00+08:00</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>A-MIX</t>
+          <t>CURE-07</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>QC 取樣</t>
+          <t>入模</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>qc</t>
+          <t>curing</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>CURI-早2</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>#L-301</t>
+          <t>#S-101</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>門尼黏度 62，合格</t>
+          <t>小胎入模，128°C，預計 24 h</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-02T16:14:00+08:00</t>
+          <t>2026-10-02T15:40:00+08:00</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>CURE-07</t>
+          <t>A-MIX</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>入模</t>
+          <t>QC 取樣</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>curing</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>CURI-中1</t>
+          <t>qc</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>#M-201</t>
+          <t>#L-301</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>中胎入模，128°C，預計 28 h</t>
+          <t>門尼黏度 62，合格</t>
         </is>
       </c>
     </row>

--- a/data/orders_seed.xlsx
+++ b/data/orders_seed.xlsx
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H8"/>
+  <dimension ref="A1:H11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -467,7 +467,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>#S-101</t>
+          <t>SO-001</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -476,10 +476,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="D2" t="n">
-        <v>38</v>
+        <v>21</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -488,12 +488,12 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>南亞堆高機</t>
+          <t>客戶A</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>MD-S101</t>
+          <t>MD-SO-001</t>
         </is>
       </c>
       <c r="H2" t="n">
@@ -503,33 +503,33 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>#S-102</t>
+          <t>SO-002</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>M</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-11-09</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>台灣搬運車</t>
+          <t>客戶B</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>MD-S102</t>
+          <t>MD-SO-002</t>
         </is>
       </c>
       <c r="H3" t="n">
@@ -539,33 +539,33 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>#M-201</t>
+          <t>SO-003</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>L</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>高雄港機具</t>
+          <t>客戶C</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>MD-M201</t>
+          <t>MD-SO-003</t>
         </is>
       </c>
       <c r="H4" t="n">
@@ -575,33 +575,33 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>#M-202</t>
+          <t>SO-004</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>S</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>50</v>
+        <v>19</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-11-17</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>東元物流</t>
+          <t>客戶D</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>MD-M202</t>
+          <t>MD-SO-004</t>
         </is>
       </c>
       <c r="H5" t="n">
@@ -611,33 +611,33 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>#L-301</t>
+          <t>SO-005</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>M</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>59</v>
+        <v>45</v>
       </c>
       <c r="D6" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-12-24</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>台中港務</t>
+          <t>客戶D</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>MD-L301</t>
+          <t>MD-SO-005</t>
         </is>
       </c>
       <c r="H6" t="n">
@@ -647,7 +647,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>#A-311</t>
+          <t>SO-006</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -656,34 +656,34 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>台塑工業車輛</t>
+          <t>客戶E</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>#A-311</t>
+          <t>MD-SO-006</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>#L-302</t>
+          <t>SO-007</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -692,28 +692,136 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>41</v>
+        <v>80</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-12-02</t>
+          <t>2027-01-03</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>中鋼運輸</t>
+          <t>客戶E</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>MD-L302</t>
+          <t>MD-SO-007</t>
         </is>
       </c>
       <c r="H8" t="n">
         <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>SO-008</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>10</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>客戶F</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>MD-SO-008</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>SO-009</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>5</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>2026-11-10</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>客戶G</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>MD-SO-009</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>#A-311</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>1</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>台塑工業車輛</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>#A-311</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -3140,7 +3248,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H12"/>
+  <dimension ref="A1:H9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3188,12 +3296,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>J-CURE-01-10030012</t>
+          <t>J-CURE-03-10020320</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>#S-101</t>
+          <t>SO-001</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -3203,17 +3311,17 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>CURE-01</t>
+          <t>CURE-03</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>MD-S101</t>
+          <t>MD-SO-001</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-10-03T00:12:00+08:00</t>
+          <t>2026-10-02T03:20:00+08:00</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -3226,12 +3334,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>J-CURE-02-10022012</t>
+          <t>J-CURE-04-10020430</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>#S-101</t>
+          <t>SO-001</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -3241,17 +3349,17 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>CURE-02</t>
+          <t>CURE-04</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>MD-S101</t>
+          <t>MD-SO-001</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-10-02T20:12:00+08:00</t>
+          <t>2026-10-02T04:30:00+08:00</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -3264,12 +3372,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>J-CURE-03-10021612</t>
+          <t>J-CURE-05-10020910</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>#S-101</t>
+          <t>SO-001</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -3279,17 +3387,17 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>CURE-03</t>
+          <t>CURE-05</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>MD-S101</t>
+          <t>MD-SO-001</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-10-02T16:12:00+08:00</t>
+          <t>2026-10-02T09:10:00+08:00</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -3302,12 +3410,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>J-CURE-04-10021212</t>
+          <t>J-CURE-06-10021040</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>#S-101</t>
+          <t>SO-001</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -3317,17 +3425,17 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>CURE-04</t>
+          <t>CURE-06</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>MD-S101</t>
+          <t>MD-SO-001</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-10-02T12:12:00+08:00</t>
+          <t>2026-10-02T10:40:00+08:00</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -3340,12 +3448,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J-CURE-05-10020812</t>
+          <t>J-CURE-07-10021150</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>#S-101</t>
+          <t>SO-001</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -3355,17 +3463,17 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>CURE-05</t>
+          <t>CURE-07</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>MD-S101</t>
+          <t>MD-SO-001</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-10-02T08:12:00+08:00</t>
+          <t>2026-10-02T11:50:00+08:00</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -3378,36 +3486,36 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J-CURE-06-10020512</t>
+          <t>J-CURE-08-10021630</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>#S-101</t>
+          <t>SO-002</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>M</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>CURE-06</t>
+          <t>CURE-08</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>MD-S101</t>
+          <t>MD-SO-002</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-10-02T05:12:00+08:00</t>
+          <t>2026-10-02T16:30:00+08:00</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="H7" t="n">
         <v>1</v>
@@ -3416,36 +3524,36 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J-CURE-07-10021150</t>
+          <t>J-CURE-09-10022130</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>#S-101</t>
+          <t>SO-002</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>M</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>CURE-07</t>
+          <t>CURE-09</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>MD-S101</t>
+          <t>MD-SO-002</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-10-02T11:50:00+08:00</t>
+          <t>2026-10-02T21:30:00+08:00</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="H8" t="n">
         <v>1</v>
@@ -3454,12 +3562,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>J-CURE-08-10020612</t>
+          <t>J-CURE-11-10012200</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>#L-301</t>
+          <t>SO-003</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -3469,137 +3577,23 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>CURE-08</t>
+          <t>CURE-11</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>MD-L301</t>
+          <t>MD-SO-003</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-10-02T06:12:00+08:00</t>
+          <t>2026-10-01T22:00:00+08:00</t>
         </is>
       </c>
       <c r="G9" t="n">
         <v>34</v>
       </c>
       <c r="H9" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>J-CURE-09-10020212</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>#M-201</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>CURE-09</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>MD-M201</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>2026-10-02T02:12:00+08:00</t>
-        </is>
-      </c>
-      <c r="G10" t="n">
-        <v>28</v>
-      </c>
-      <c r="H10" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>J-CURE-10-10022012</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>#L-301</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>CURE-10</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>MD-L301</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>2026-10-02T20:12:00+08:00</t>
-        </is>
-      </c>
-      <c r="G11" t="n">
-        <v>34</v>
-      </c>
-      <c r="H11" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>J-CURE-11-10021612</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>#M-201</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>CURE-11</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>MD-M201</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>2026-10-02T16:12:00+08:00</t>
-        </is>
-      </c>
-      <c r="G12" t="n">
-        <v>28</v>
-      </c>
-      <c r="H12" t="n">
         <v>1</v>
       </c>
     </row>
@@ -3906,49 +3900,44 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-02T02:12:00+08:00</t>
+          <t>2026-10-02T10:05:00+08:00</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>CURE-09</t>
+          <t>A-BIGOPEN</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>入模</t>
+          <t>巡檢</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>body</t>
+          <t>bigopen</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>BODY-夜1</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>#M-201</t>
+          <t>BIGO-早1</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>中胎入模，128°C，預計 28 h</t>
+          <t>膠溫 96°C，水流正常</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-02T06:12:00+08:00</t>
+          <t>2026-10-02T11:50:00+08:00</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>CURE-08</t>
+          <t>CURE-07</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -3968,56 +3957,56 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>#L-301</t>
+          <t>SO-001</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>大胎入模，128°C，預計 34 h</t>
+          <t>小胎入模，128°C，預計 24 h</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-02T10:05:00+08:00</t>
+          <t>2026-10-02T15:40:00+08:00</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>A-BIGOPEN</t>
+          <t>A-MIX</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>巡檢</t>
+          <t>QC 取樣</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>bigopen</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>BIGO-早1</t>
+          <t>qc</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>#L-301</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>膠溫 96°C，水流正常</t>
+          <t>門尼黏度 62，合格</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-02T11:50:00+08:00</t>
+          <t>2026-10-02T16:30:00+08:00</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>CURE-07</t>
+          <t>CURE-08</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -4032,88 +4021,93 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>CURI-早2</t>
+          <t>CURI-中1</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>#S-101</t>
+          <t>SO-002</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>小胎入模，128°C，預計 24 h</t>
+          <t>中胎入模，128°C，預計 28 h</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-02T15:40:00+08:00</t>
+          <t>2026-10-02T18:00:00+08:00</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>A-MIX</t>
+          <t>CURE-03</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>QC 取樣</t>
+          <t>保養</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>qc</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>#L-301</t>
+          <t>maintenance</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>門尼黏度 62，合格</t>
+          <t>更換疏水閥墊片</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-02T18:00:00+08:00</t>
+          <t>2026-10-02T20:12:00+08:00</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>CURE-03</t>
+          <t>CURE-10</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>保養</t>
+          <t>入模</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>maintenance</t>
+          <t>body</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>BODY-夜1</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>#L-301</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>更換疏水閥墊片</t>
+          <t>大胎入模，128°C，預計 34 h</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-02T20:12:00+08:00</t>
+          <t>2026-10-02T21:30:00+08:00</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>CURE-10</t>
+          <t>CURE-09</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -4133,12 +4127,12 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>#L-301</t>
+          <t>SO-002</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>大胎入模，128°C，預計 34 h</t>
+          <t>中胎入模，128°C，預計 28 h</t>
         </is>
       </c>
     </row>

--- a/data/orders_seed.xlsx
+++ b/data/orders_seed.xlsx
@@ -488,7 +488,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>客戶A</t>
+          <t>福氣輪業股份有限公司</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -524,7 +524,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>客戶B</t>
+          <t>金旺來工業社</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -560,7 +560,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>客戶C</t>
+          <t>大力出奇蹟實業有限公司</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -596,7 +596,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>客戶D</t>
+          <t>永固機械股份有限公司</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -632,7 +632,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>客戶D</t>
+          <t>永固機械股份有限公司</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -668,7 +668,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>客戶E</t>
+          <t>黑狗兄輪業商社</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>客戶E</t>
+          <t>黑狗兄輪業商社</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -740,7 +740,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>客戶F</t>
+          <t>好運輪輪來企業社</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -776,7 +776,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>客戶G</t>
+          <t>鐵牛運搬股份有限公司</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -812,7 +812,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>台塑工業車輛</t>
+          <t>永固機械股份有限公司</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
